--- a/data/LifeICICISmartPlusTestData.xlsx
+++ b/data/LifeICICISmartPlusTestData.xlsx
@@ -873,7 +873,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -897,19 +897,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin"/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -922,7 +909,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -936,13 +923,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1457,7 +1441,7 @@
         <v>30</v>
       </c>
       <c r="F3" s="2">
-        <v>987992</v>
+        <v>260060</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>38</v>
@@ -1642,7 +1626,9 @@
       <c r="E6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2">
+        <v>255055</v>
+      </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
       </c>
@@ -1771,7 +1757,7 @@
         <v>30</v>
       </c>
       <c r="F8" s="2">
-        <v>987992</v>
+        <v>260060</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
@@ -1834,7 +1820,9 @@
       <c r="E9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2">
+        <v>255055</v>
+      </c>
       <c r="G9" s="2" t="s">
         <v>31</v>
       </c>
@@ -1897,7 +1885,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="2">
-        <v>987992</v>
+        <v>260060</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
@@ -3241,7 +3229,7 @@
       <c r="Z30" s="2"/>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
+      <c r="B31" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V39"/>
@@ -3263,386 +3251,386 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="2" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="3" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="8"/>
     </row>
     <row r="9" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="8"/>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="8"/>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="8"/>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="8"/>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="8"/>
     </row>
     <row r="15" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="9"/>
+      <c r="D15" s="8"/>
     </row>
     <row r="16" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D16" s="9"/>
+      <c r="D16" s="8"/>
     </row>
     <row r="17" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D18" s="9"/>
+      <c r="D18" s="8"/>
     </row>
     <row r="19" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D19" s="9"/>
+      <c r="D19" s="8"/>
     </row>
     <row r="20" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D20" s="9"/>
+      <c r="D20" s="8"/>
     </row>
     <row r="21" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D21" s="9"/>
+      <c r="D21" s="8"/>
     </row>
     <row r="22" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D22" s="9"/>
+      <c r="D22" s="8"/>
     </row>
     <row r="23" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="8"/>
     </row>
     <row r="24" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D24" s="9"/>
+      <c r="D24" s="8"/>
     </row>
     <row r="25" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D25" s="9"/>
+      <c r="D25" s="8"/>
     </row>
     <row r="26" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D26" s="9"/>
+      <c r="D26" s="8"/>
     </row>
     <row r="27" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="8" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D28" s="9"/>
+      <c r="D28" s="8"/>
     </row>
     <row r="29" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>196</v>
       </c>
     </row>
@@ -3664,74 +3652,74 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="2" ht="33.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="3" ht="51" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="4" ht="51" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="5" ht="51" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="6" ht="33.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="7" ht="68.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="8" ht="33.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="9" ht="51" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>214</v>
       </c>
     </row>
@@ -3809,13 +3797,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>229</v>
       </c>
     </row>
@@ -3931,13 +3919,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>233</v>
       </c>
     </row>

--- a/data/LifeICICISmartPlusTestData.xlsx
+++ b/data/LifeICICISmartPlusTestData.xlsx
@@ -2281,7 +2281,7 @@
         <v>30</v>
       </c>
       <c r="F16" s="2">
-        <v>987992</v>
+        <v>260060</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>31</v>
@@ -2885,7 +2885,7 @@
         <v>30</v>
       </c>
       <c r="F25" s="2">
-        <v>987992</v>
+        <v>260060</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -3005,7 +3005,7 @@
         <v>30</v>
       </c>
       <c r="F27" s="2">
-        <v>987992</v>
+        <v>260060</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>31</v>
